--- a/data/externalStats/File1/RPT_RPT7432825158817CT_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT7432825158817CT_externalStats.xlsx
@@ -2057,7 +2057,7 @@
         <v>35031</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>738222.6000000001</v>
+        <v>738222.6</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>752400</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>4485152.572008873</v>
+        <v>9149963.910613641</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>6502.991610080123</v>
+        <v>6502.991610080124</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2134,13 +2134,13 @@
         <v>6424</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>370464.4899999999</v>
+        <v>370464.49</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>492332</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>57.66881849315067</v>
+        <v>57.6688184931507</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>76.63947696139476</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>2493997.647431938</v>
+        <v>5062555.365522953</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>3830.380533297244</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1383553.339862024</v>
+        <v>2941396.867403055</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>2792.287975748667</v>
@@ -2294,7 +2294,7 @@
         <v>1257088</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>26.86525550427844</v>
+        <v>26.86525550427843</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>30.21555619651956</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1078908.842917003</v>
+        <v>2293730.931317767</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>3519.787725747213</v>
+        <v>3519.787725747212</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -2365,7 +2365,7 @@
         <v>514</v>
       </c>
       <c r="E29" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F29" s="61" t="n">
         <v>18866</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>823490.1778661158</v>
+        <v>1671618.482996262</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>184.281043569371</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>597696.7696467171</v>
+        <v>1270687.117904037</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1210.913003344472</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>542056.5439703228</v>
+        <v>1100330.959718119</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>65.20728661725711</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>510027.4491912912</v>
+        <v>1035302.580227402</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>758.1776779944734</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>488844.4894706476</v>
+        <v>992303.3791247767</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>660.8714519417067</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>382233.8253246066</v>
+        <v>812618.7433708962</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>682.8589505041772</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>347364.5034530131</v>
+        <v>738487.5110095892</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>1022.657967392292</v>
@@ -2884,13 +2884,13 @@
         <v>441233</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35611716.065</v>
+        <v>35611716.06500001</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25007081</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.70954816389526</v>
+        <v>80.70954816389528</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.67545491837646</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>241083.2110117621</v>
+        <v>489379.4271009141</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>79.61792242790725</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>219778.2487140274</v>
+        <v>446332.0737118208</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>29.43111557345097</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>182113.6173087421</v>
+        <v>387168.6100058801</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>183.2779633371303</v>
@@ -3136,19 +3136,19 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>OTEZLA</t>
+          <t>ANORO ELLIPTA</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>166879.3396745522</v>
+        <v>343586.3194110444</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>74.17039169135714</v>
+        <v>457.5481782043609</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -3203,19 +3203,19 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ANORO ELLIPTA</t>
+          <t>OTEZLA</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>161669.0397210226</v>
+        <v>338751.5675694513</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>457.5481782043609</v>
+        <v>74.17039169135714</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>150312.7407606285</v>
+        <v>319560.8091612657</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>388.1556750446662</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>136226.2807151814</v>
+        <v>276528.3361404674</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>33.82403667607072</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>111582.8160452323</v>
+        <v>237222.0398847714</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>326.6424257603529</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>109743.4473794957</v>
+        <v>233311.5919999529</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>41.55721261714001</v>
@@ -3553,7 +3553,7 @@
         <v>514</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>18866</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>7978022.158102749</v>
+        <v>16240125.23548877</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>11752.69585598702</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>2784729.635457475</v>
+        <v>5920141.987353</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>6467.382142564416</v>
+        <v>6467.382142564417</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2360534.695451892</v>
+        <v>4791894.583313752</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>620.1207962008932</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1129048.714701964</v>
+        <v>2400326.938534217</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>3971.510183973837</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>382233.8253246067</v>
+        <v>812618.7433708962</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>929.8503331028037</v>
@@ -3989,7 +3989,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>41.17788482492599</v>
@@ -3998,16 +3998,16 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -4016,7 +4016,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V54" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W54" s="131" t="n">
         <v>2685.600441370127</v>
@@ -4028,21 +4028,21 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>295536.4981306852</v>
+        <v>620480.202005833</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>550.7164005935906</v>
+        <v>224.8351759542703</v>
       </c>
     </row>
     <row r="55">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>291857.0646882378</v>
+        <v>606566.3063139846</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>224.8351759542703</v>
+        <v>550.7164005935906</v>
       </c>
     </row>
     <row r="56">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>164356.4629033951</v>
+        <v>333626.4947910959</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>1644.951949865332</v>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>157448.360982624</v>
+        <v>329485.6904945093</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>458.7163804477967</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>0</v>
@@ -4322,13 +4322,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>126310.8446137636</v>
+        <v>268533.4290783537</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>473.1751484562236</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>114390.3931232967</v>
+        <v>232200.5792856024</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>338.1913773636248</v>
@@ -4502,7 +4502,7 @@
         <v>20.903453733182</v>
       </c>
       <c r="V60" s="130" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="W60" s="131" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="132" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="AE60" s="121" t="n">
         <v>12</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>91227.10757147713</v>
+        <v>192987.5034541888</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>272.1384864083959</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>73853.09801189994</v>
+        <v>155755.7825707083</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>130.8563425551474</v>
@@ -4637,7 +4637,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>3.774092554166141</v>
@@ -4646,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>303.2145528003117</v>
@@ -4655,7 +4655,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>564.9133635784891</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>68493.04257426698</v>
+        <v>142090.6665193275</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>262.8797756634193</v>
@@ -4715,7 +4715,7 @@
         <v>5553</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1802.821324481974</v>
+        <v>1802.82132448198</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>1753.114204203743</v>
@@ -4727,22 +4727,22 @@
         <v>2844.950696784313</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>6429.36925984275</v>
+        <v>6429.369259842755</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>1851.880461115068</v>
+        <v>1851.88046111507</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>3076.857772465649</v>
+        <v>3076.857772465648</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>6766.011556755312</v>
+        <v>6766.011556755315</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>1901.212535840979</v>
@@ -4754,10 +4754,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3301.979441896157</v>
+        <v>3301.979441896156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7099.933196522159</v>
+        <v>7099.933196522158</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>64589.03808480527</v>
+        <v>137314.5427918008</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>109.1334772812495</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>63735.35805642563</v>
+        <v>135499.6422101645</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>367.361014420474</v>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>10362.76294094245</v>
@@ -4900,22 +4900,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q65" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R65" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S65" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W65" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X65" s="134" t="n">
         <v>52.89522154413101</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>63724.53791713162</v>
+        <v>135476.638887555</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>233.7819431372323</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>43853.60938262549</v>
+        <v>93231.58388330411</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>255.3343213704184</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>42753.97205037576</v>
+        <v>90893.78474598905</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>49.17758916476652</v>
@@ -5126,10 +5126,10 @@
         <v>15667</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>16726.1744960469</v>
+        <v>16726.17449604691</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>200.2485681823899</v>
@@ -5138,7 +5138,7 @@
         <v>3035.538750812163</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>38046.13205183197</v>
+        <v>38046.13205183198</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>13288.69061109529</v>
@@ -5150,7 +5150,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>3271.254361623844</v>
+        <v>3271.254361623843</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>30705.86223329496</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>37518.87483107837</v>
+        <v>77995.51205759637</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>336.433206483451</v>
@@ -5552,7 +5552,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>0</v>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V74" s="130" t="n">
         <v>9.887007747403397</v>
@@ -5805,7 +5805,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="130" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="K78" s="131" t="n">
         <v>0</v>
@@ -5817,10 +5817,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="132" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="P78" s="130" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="Q78" s="131" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="132" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="V78" s="130" t="n">
         <v>9.398797005461862</v>
@@ -6611,7 +6611,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>41.17788482492599</v>
@@ -6620,16 +6620,16 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V90" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W90" s="131" t="n">
         <v>2685.600441370127</v>
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
     </row>
     <row r="91">
@@ -6757,7 +6757,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>0</v>
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V92" s="130" t="n">
         <v>9.887007747403397</v>
@@ -6879,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L94" s="131" t="n">
         <v>0</v>
@@ -6888,13 +6888,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>30.30547604487107</v>
       </c>
       <c r="P96" s="130" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="Q96" s="131" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="132" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="V96" s="130" t="n">
         <v>29.43890635513617</v>
@@ -7147,7 +7147,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>3.774092554166141</v>
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>303.2145528003117</v>
@@ -7165,7 +7165,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>564.9133635784891</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
     </row>
     <row r="99">
@@ -7211,7 +7211,7 @@
         <v>5955</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1810.995396542639</v>
+        <v>1810.995396542643</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1753.114204203743</v>
@@ -7223,25 +7223,25 @@
         <v>3387.161343351757</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>6979.753978470859</v>
+        <v>6979.753978470862</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>1866.55260272007</v>
+        <v>1866.552602720072</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3691.21780479876</v>
+        <v>3691.217804798759</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>7395.043730693425</v>
+        <v>7395.043730693427</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1924.132424633852</v>
+        <v>1924.132424633854</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1866.517853908823</v>
@@ -7250,10 +7250,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>4002.083765415841</v>
+        <v>4002.08376541584</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>7822.957408834715</v>
+        <v>7822.957408834716</v>
       </c>
     </row>
     <row r="100">
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>10362.76294094245</v>
@@ -7368,22 +7368,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q101" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R101" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S101" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W101" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X101" s="134" t="n">
         <v>52.89522154413101</v>
@@ -7553,7 +7553,7 @@
         <v>16747.82759709495</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>200.2485681823899</v>
@@ -7562,7 +7562,7 @@
         <v>3577.749397379607</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>39152.2064460149</v>
+        <v>39152.20644601491</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>13321.20947909905</v>
@@ -7574,7 +7574,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>3885.614393956954</v>
+        <v>3885.614393956953</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>31967.10116596494</v>
@@ -7589,7 +7589,7 @@
         <v>129.0666188664547</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>4201.890485304369</v>
+        <v>4201.890485304368</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>29537.67339702922</v>
@@ -8581,7 +8581,7 @@
         <v>35031</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>738222.6000000001</v>
+        <v>738222.6</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>752400</v>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>5730185.213893273</v>
+        <v>11856007.72215059</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>8128.782825788128</v>
+        <v>8128.782825788127</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8658,13 +8658,13 @@
         <v>6424</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>370464.4899999999</v>
+        <v>370464.49</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>492332</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>57.66881849315067</v>
+        <v>57.6688184931507</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>76.63947696139476</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>2905703.945179558</v>
+        <v>5968763.573542986</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>4290.244858665416</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1497192.522978476</v>
+        <v>3244663.520605433</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>2920.956605671166</v>
@@ -8818,7 +8818,7 @@
         <v>1257088</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>26.86525550427844</v>
+        <v>26.86525550427843</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>30.21555619651956</v>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1309725.473527205</v>
+        <v>2838391.456502413</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>4153.349516381711</v>
@@ -8889,7 +8889,7 @@
         <v>514</v>
       </c>
       <c r="E29" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F29" s="61" t="n">
         <v>18866</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>848824.7660158189</v>
+        <v>1743596.03678567</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>193.3559319210432</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>693324.4762213475</v>
+        <v>1424178.29609311</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>79.45136733018217</v>
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>949.3265373200994</v>
+        <v>949.3265373200995</v>
       </c>
     </row>
     <row r="31">
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>648887.7724523137</v>
+        <v>1406246.993575995</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1266.711874538585</v>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>581866.6305464627</v>
+        <v>1195243.704998757</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>849.15899935381</v>
+        <v>849.1589993538101</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>569513.1356299943</v>
+        <v>1169867.723186952</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>740.1760261747115</v>
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>396900.49877657</v>
+        <v>860148.9453931447</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>684.9758132507401</v>
+        <v>684.9758132507402</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>378327.0112208607</v>
+        <v>819897.1296797323</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>1107.384612270476</v>
@@ -9408,13 +9408,13 @@
         <v>441233</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35611716.065</v>
+        <v>35611716.06500001</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25007081</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.70954816389526</v>
+        <v>80.70954816389528</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.67545491837646</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>311534.8095318336</v>
+        <v>639932.8588986534</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>96.74290112363829</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>289430.6016931018</v>
+        <v>594545.9703243282</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>35.66315429612921</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>195856.8845970606</v>
+        <v>424454.2227924595</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>189.0163963692158</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>179294.9810259263</v>
+        <v>388353.2887468641</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>488.7541251073535</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>176848.2935584367</v>
+        <v>363269.3061114717</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>75.56034483165317</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>164021.2774841714</v>
+        <v>355461.2032106997</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>406.0418885507245</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>155432.1673017843</v>
+        <v>319277.8082671397</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>37.11859268194824</v>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>120005.7060501754</v>
+        <v>260072.1889198886</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>336.8254182951961</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>117416.7466246607</v>
+        <v>254461.4861709971</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>42.85836894418266</v>
@@ -10077,7 +10077,7 @@
         <v>514</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>18866</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>9787268.925249288</v>
+        <v>20189882.72387929</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>14008.39889028728</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3021756.476333831</v>
+        <v>6548436.899239033</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>6765.399111693786</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2731891.871567022</v>
+        <v>5611677.845662771</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>665.9304373242285</v>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1372354.762059194</v>
+        <v>2974119.470570339</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>4686.382017089129</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>396900.49877657</v>
+        <v>860148.9453931447</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>763.055433826904</v>
@@ -10513,7 +10513,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>41.17788482492599</v>
@@ -10522,16 +10522,16 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V54" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W54" s="131" t="n">
         <v>2685.600441370127</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -10563,10 +10563,10 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>335625.1182548095</v>
+        <v>700273.6222124852</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>595.1702284495053</v>
+        <v>595.1702284495052</v>
       </c>
     </row>
     <row r="55">
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>313273.6312217214</v>
+        <v>678915.7089634567</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>231.8747653133985</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>164235.0823963753</v>
+        <v>337364.1622821072</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>1570.304030380443</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>141327.5340875603</v>
+        <v>301313.7661440386</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>381.0225771768046</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>0</v>
@@ -10846,13 +10846,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>130132.197755448</v>
+        <v>282017.9692544354</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>471.8360627860924</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>129200.2451049726</v>
+        <v>267891.0640798375</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>360.2208185598055</v>
@@ -11026,7 +11026,7 @@
         <v>20.903453733182</v>
       </c>
       <c r="V60" s="130" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="W60" s="131" t="n">
         <v>0</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="132" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="AE60" s="121" t="n">
         <v>12</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>95696.14946152319</v>
+        <v>206576.1527820975</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>269.4497581626809</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>88833.05115562616</v>
+        <v>191014.1854414143</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>147.5496861749075</v>
@@ -11161,7 +11161,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>3.774092554166141</v>
@@ -11170,7 +11170,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>303.2145528003117</v>
@@ -11179,7 +11179,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -11188,7 +11188,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>564.9133635784891</v>
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>68171.37269510971</v>
+        <v>147738.6259539847</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>108.3771822836905</v>
@@ -11239,7 +11239,7 @@
         <v>5553</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1802.821324481974</v>
+        <v>1802.82132448198</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>1753.114204203743</v>
@@ -11251,22 +11251,22 @@
         <v>2844.950696784313</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>6429.36925984275</v>
+        <v>6429.369259842755</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>1851.880461115068</v>
+        <v>1851.88046111507</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>3076.857772465649</v>
+        <v>3076.857772465648</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>6766.011556755312</v>
+        <v>6766.011556755315</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>1901.212535840979</v>
@@ -11278,10 +11278,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3301.979441896157</v>
+        <v>3301.979441896156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7099.933196522159</v>
+        <v>7099.933196522158</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>62932.61888608666</v>
+        <v>136385.3810528183</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>217.5224089920378</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>60405.02048118969</v>
+        <v>130907.6577719176</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>318.1541299432944</v>
@@ -11406,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>10362.76294094245</v>
@@ -11424,22 +11424,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q65" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R65" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S65" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W65" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X65" s="134" t="n">
         <v>52.89522154413101</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>42894.4453073018</v>
+        <v>92959.3487738837</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>231.8818639525455</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>42557.37495223103</v>
+        <v>92228.86163332553</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>46.22939269433876</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>36080.02107168931</v>
+        <v>76194.63746533614</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>320.7227882854055</v>
@@ -11650,10 +11650,10 @@
         <v>15667</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>16726.1744960469</v>
+        <v>16726.17449604691</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>200.2485681823899</v>
@@ -11662,7 +11662,7 @@
         <v>3035.538750812163</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>38046.13205183197</v>
+        <v>38046.13205183198</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>13288.69061109529</v>
@@ -11674,7 +11674,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>3271.254361623844</v>
+        <v>3271.254361623843</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>30705.86223329496</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>34494.97670319192</v>
+        <v>74756.31278889984</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>47.58497061758919</v>
@@ -12076,7 +12076,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V74" s="130" t="n">
         <v>9.887007747403397</v>
@@ -12329,7 +12329,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="130" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="K78" s="131" t="n">
         <v>0</v>
@@ -12341,10 +12341,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="132" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="P78" s="130" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="Q78" s="131" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="132" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="V78" s="130" t="n">
         <v>9.398797005461862</v>
@@ -13135,7 +13135,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>41.17788482492599</v>
@@ -13144,16 +13144,16 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -13162,7 +13162,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V90" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W90" s="131" t="n">
         <v>2685.600441370127</v>
@@ -13174,7 +13174,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
     </row>
     <row r="91">
@@ -13281,7 +13281,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V92" s="130" t="n">
         <v>9.887007747403397</v>
@@ -13403,7 +13403,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L94" s="131" t="n">
         <v>0</v>
@@ -13412,13 +13412,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -13549,7 +13549,7 @@
         <v>30.30547604487107</v>
       </c>
       <c r="P96" s="130" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="Q96" s="131" t="n">
         <v>0</v>
@@ -13561,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="132" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="V96" s="130" t="n">
         <v>29.43890635513617</v>
@@ -13671,7 +13671,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>3.774092554166141</v>
@@ -13680,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>303.2145528003117</v>
@@ -13689,7 +13689,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -13698,7 +13698,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>564.9133635784891</v>
@@ -13710,7 +13710,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
     </row>
     <row r="99">
@@ -13735,7 +13735,7 @@
         <v>5955</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1810.995396542639</v>
+        <v>1810.995396542643</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1753.114204203743</v>
@@ -13747,25 +13747,25 @@
         <v>3387.161343351757</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>6979.753978470859</v>
+        <v>6979.753978470862</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>1866.55260272007</v>
+        <v>1866.552602720072</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3691.21780479876</v>
+        <v>3691.217804798759</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>7395.043730693425</v>
+        <v>7395.043730693427</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1924.132424633852</v>
+        <v>1924.132424633854</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1866.517853908823</v>
@@ -13774,10 +13774,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>4002.083765415841</v>
+        <v>4002.08376541584</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>7822.957408834715</v>
+        <v>7822.957408834716</v>
       </c>
     </row>
     <row r="100">
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -13874,7 +13874,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>10362.76294094245</v>
@@ -13892,22 +13892,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q101" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R101" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S101" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W101" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X101" s="134" t="n">
         <v>52.89522154413101</v>
@@ -14077,7 +14077,7 @@
         <v>16747.82759709495</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>200.2485681823899</v>
@@ -14086,7 +14086,7 @@
         <v>3577.749397379607</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>39152.2064460149</v>
+        <v>39152.20644601491</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>13321.20947909905</v>
@@ -14098,7 +14098,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>3885.614393956954</v>
+        <v>3885.614393956953</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>31967.10116596494</v>
@@ -14113,7 +14113,7 @@
         <v>129.0666188664547</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>4201.890485304369</v>
+        <v>4201.890485304368</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>29537.67339702922</v>
@@ -15105,7 +15105,7 @@
         <v>35031</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>738222.6000000001</v>
+        <v>738222.6</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>752400</v>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7105821.769012147</v>
+        <v>14878914.71770434</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>9754.527377416773</v>
+        <v>9754.527377416774</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15182,13 +15182,13 @@
         <v>6424</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>370464.4899999999</v>
+        <v>370464.49</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>492332</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>57.66881849315067</v>
+        <v>57.6688184931507</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>76.63947696139476</v>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>3383894.153193892</v>
+        <v>7036020.811467695</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>4762.171793118613</v>
+        <v>4762.171793118612</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -15303,10 +15303,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1643153.743130789</v>
+        <v>3597509.618513254</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>3055.554286060492</v>
+        <v>3055.554286060493</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -15342,7 +15342,7 @@
         <v>1257088</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>26.86525550427844</v>
+        <v>26.86525550427843</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>30.21555619651956</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1612480.994699708</v>
+        <v>3530354.911920307</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>4900.952429330418</v>
@@ -15413,7 +15413,7 @@
         <v>514</v>
       </c>
       <c r="E29" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F29" s="61" t="n">
         <v>18866</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>867055.9045907295</v>
+        <v>1802881.498706146</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>198.8598248082519</v>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>854042.6315761214</v>
+        <v>1775822.817678279</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>92.42565264264738</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>713018.5283090936</v>
+        <v>1561077.911603526</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1325.081957717323</v>
@@ -15668,10 +15668,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>667647.1117400256</v>
+        <v>1388434.159418289</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>942.5664892827295</v>
+        <v>942.5664892827294</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>663237.6202753057</v>
+        <v>1379048.364973481</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>821.59538905393</v>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>415906.9490123874</v>
+        <v>910583.8426462271</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>685.3046016411006</v>
+        <v>685.3046016411005</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>396900.6438823214</v>
+        <v>825281.0734479192</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>114.8941218067131</v>
@@ -15932,13 +15932,13 @@
         <v>441233</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35611716.065</v>
+        <v>35611716.06500001</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25007081</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.70954816389526</v>
+        <v>80.70954816389528</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.67545491837646</v>
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>378074.8853323186</v>
+        <v>785344.4008914226</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>42.50120750086902</v>
+        <v>42.50120750086903</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>213345.6468087838</v>
+        <v>467097.5066521454</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>194.7114603918203</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>197476.6019811068</v>
+        <v>432089.1431667888</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>511.2759151923002</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>181275.4050826702</v>
+        <v>396883.1377532788</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>424.7522987751418</v>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>168220.6477168611</v>
+        <v>349783.5512835234</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>38.12369376989282</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>130081.0722402474</v>
+        <v>284798.6139624178</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>345.2595267693078</v>
@@ -16405,19 +16405,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>EMGALITY</t>
+          <t>ZENPEP</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>127471.165201303</v>
+        <v>278192.2814565949</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>237.6692890931074</v>
+        <v>44.14969160047089</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -16482,19 +16482,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>ZENPEP</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>127063.6459825254</v>
+        <v>265736.2625463491</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>44.14969160047089</v>
+        <v>237.6692890931074</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>113557.6562659855</v>
+        <v>248622.3595208568</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>394.2773828417476</v>
@@ -16601,7 +16601,7 @@
         <v>514</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>18866</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>11820600.65422137</v>
+        <v>24682418.05356381</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>16280.90120901083</v>
@@ -16754,14 +16754,14 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>2911292.845521264</v>
+        <v>6177871.714213696</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>677.1365843665978</v>
+        <v>5980.547077325682</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -16800,14 +16800,14 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2821848.776066676</v>
+        <v>6052700.021715601</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>5980.547077325682</v>
+        <v>677.1365843665978</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1691834.100561341</v>
+        <v>3704090.061652672</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>5529.93078016517</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>415906.9490123874</v>
+        <v>910583.842646227</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>705.9705007929631</v>
@@ -17037,7 +17037,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>41.17788482492599</v>
@@ -17046,16 +17046,16 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -17064,7 +17064,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V54" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W54" s="131" t="n">
         <v>2685.600441370127</v>
@@ -17076,7 +17076,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>384511.3264351888</v>
+        <v>811257.9803787267</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>641.5696994594288</v>
+        <v>641.5696994594286</v>
       </c>
     </row>
     <row r="55">
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>340409.2927913092</v>
+        <v>745289.7881087405</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>238.8611519922912</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>164477.1319843272</v>
+        <v>341975.3153298001</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>1498.823790917525</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>153722.7534397969</v>
+        <v>331867.2143621233</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>376.8286549127328</v>
@@ -17361,7 +17361,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>0</v>
@@ -17370,13 +17370,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>135513.0717390803</v>
+        <v>296691.3966837577</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>469.5665313240913</v>
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>107456.3323281224</v>
+        <v>232886.4631993899</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>166.0435638400704</v>
@@ -17550,7 +17550,7 @@
         <v>20.903453733182</v>
       </c>
       <c r="V60" s="130" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="W60" s="131" t="n">
         <v>0</v>
@@ -17562,7 +17562,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="132" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="AE60" s="121" t="n">
         <v>12</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>101481.8901448901</v>
+        <v>221065.8408672293</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>266.7875945520336</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>61246.32032150245</v>
+        <v>128525.2355527735</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>257.3451657421735</v>
@@ -17685,7 +17685,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>3.774092554166141</v>
@@ -17694,7 +17694,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>303.2145528003117</v>
@@ -17703,7 +17703,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -17712,7 +17712,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>564.9133635784891</v>
@@ -17724,7 +17724,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>57882.58132104109</v>
+        <v>126727.7294759182</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>282.0331112011704</v>
@@ -17763,7 +17763,7 @@
         <v>5553</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1802.821324481974</v>
+        <v>1802.82132448198</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>1753.114204203743</v>
@@ -17775,22 +17775,22 @@
         <v>2844.950696784313</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>6429.36925984275</v>
+        <v>6429.369259842755</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>1851.880461115068</v>
+        <v>1851.88046111507</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>3076.857772465649</v>
+        <v>3076.857772465648</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>6766.011556755312</v>
+        <v>6766.011556755315</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>1901.212535840979</v>
@@ -17802,10 +17802,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3301.979441896157</v>
+        <v>3301.979441896156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7099.933196522159</v>
+        <v>7099.933196522158</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>55799.41275277953</v>
+        <v>122166.8543949131</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>193.8511492817437</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>43317.35248530962</v>
+        <v>94838.71662399062</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>43.81252004427873</v>
@@ -17930,7 +17930,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>10362.76294094245</v>
@@ -17948,22 +17948,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q65" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R65" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S65" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W65" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X65" s="134" t="n">
         <v>52.89522154413101</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>41122.84325685707</v>
+        <v>90034.0730595778</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>211.3580001741057</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>35321.44020195471</v>
+        <v>77332.52070750299</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>45.41890275507653</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>35241.66430917664</v>
+        <v>75265.23114070126</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>306.1234869626538</v>
+        <v>306.1234869626539</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -18174,10 +18174,10 @@
         <v>15667</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>16726.1744960469</v>
+        <v>16726.17449604691</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>200.2485681823899</v>
@@ -18186,7 +18186,7 @@
         <v>3035.538750812163</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>38046.13205183197</v>
+        <v>38046.13205183198</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>13288.69061109529</v>
@@ -18198,7 +18198,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>3271.254361623844</v>
+        <v>3271.254361623843</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>30705.86223329496</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>33501.81319881461</v>
+        <v>73058.81562879668</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>159.8868708811818</v>
@@ -18600,7 +18600,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>0</v>
@@ -18612,7 +18612,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V74" s="130" t="n">
         <v>9.887007747403397</v>
@@ -18853,7 +18853,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="130" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="K78" s="131" t="n">
         <v>0</v>
@@ -18865,10 +18865,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="132" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="P78" s="130" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="Q78" s="131" t="n">
         <v>0</v>
@@ -18880,7 +18880,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="132" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="V78" s="130" t="n">
         <v>9.398797005461862</v>
@@ -19659,7 +19659,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>41.17788482492599</v>
@@ -19668,16 +19668,16 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -19686,7 +19686,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V90" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W90" s="131" t="n">
         <v>2685.600441370127</v>
@@ -19698,7 +19698,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
     </row>
     <row r="91">
@@ -19805,7 +19805,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>0</v>
@@ -19817,7 +19817,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V92" s="130" t="n">
         <v>9.887007747403397</v>
@@ -19927,7 +19927,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L94" s="131" t="n">
         <v>0</v>
@@ -19936,13 +19936,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -20073,7 +20073,7 @@
         <v>30.30547604487107</v>
       </c>
       <c r="P96" s="130" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="Q96" s="131" t="n">
         <v>0</v>
@@ -20085,7 +20085,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="132" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="V96" s="130" t="n">
         <v>29.43890635513617</v>
@@ -20195,7 +20195,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>3.774092554166141</v>
@@ -20204,7 +20204,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>303.2145528003117</v>
@@ -20213,7 +20213,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -20222,7 +20222,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>564.9133635784891</v>
@@ -20234,7 +20234,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
     </row>
     <row r="99">
@@ -20259,7 +20259,7 @@
         <v>5955</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1810.995396542639</v>
+        <v>1810.995396542643</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1753.114204203743</v>
@@ -20271,25 +20271,25 @@
         <v>3387.161343351757</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>6979.753978470859</v>
+        <v>6979.753978470862</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>1866.55260272007</v>
+        <v>1866.552602720072</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3691.21780479876</v>
+        <v>3691.217804798759</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>7395.043730693425</v>
+        <v>7395.043730693427</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1924.132424633852</v>
+        <v>1924.132424633854</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1866.517853908823</v>
@@ -20298,10 +20298,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>4002.083765415841</v>
+        <v>4002.08376541584</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>7822.957408834715</v>
+        <v>7822.957408834716</v>
       </c>
     </row>
     <row r="100">
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20398,7 +20398,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>10362.76294094245</v>
@@ -20416,22 +20416,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q101" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R101" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S101" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W101" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X101" s="134" t="n">
         <v>52.89522154413101</v>
@@ -20601,7 +20601,7 @@
         <v>16747.82759709495</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>200.2485681823899</v>
@@ -20610,7 +20610,7 @@
         <v>3577.749397379607</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>39152.2064460149</v>
+        <v>39152.20644601491</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>13321.20947909905</v>
@@ -20622,7 +20622,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>3885.614393956954</v>
+        <v>3885.614393956953</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>31967.10116596494</v>
@@ -20637,7 +20637,7 @@
         <v>129.0666188664547</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>4201.890485304369</v>
+        <v>4201.890485304368</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>29537.67339702922</v>
@@ -21629,7 +21629,7 @@
         <v>35031</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>738222.6000000001</v>
+        <v>738222.6</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>752400</v>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>8733474.763056399</v>
+        <v>18557354.13596209</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>11705.41951788296</v>
@@ -21706,13 +21706,13 @@
         <v>6424</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>370464.4899999999</v>
+        <v>370464.49</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>492332</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>57.66881849315067</v>
+        <v>57.6688184931507</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>76.63947696139476</v>
@@ -21750,7 +21750,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>3905887.46228361</v>
+        <v>8242934.169993574</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>5286.010690361662</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1967647.373024347</v>
+        <v>4364901.596881898</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>5783.123866609893</v>
@@ -21866,7 +21866,7 @@
         <v>1257088</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>26.86525550427844</v>
+        <v>26.86525550427843</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>30.21555619651956</v>
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1787380.792922318</v>
+        <v>3965009.881456091</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>3196.35422756216</v>
+        <v>3196.354227562159</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -21937,7 +21937,7 @@
         <v>514</v>
       </c>
       <c r="E29" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F29" s="61" t="n">
         <v>18866</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1038430.264055534</v>
+        <v>2191520.716910724</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>107.1309756533883</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>898145.1573016973</v>
+        <v>1895460.665151076</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>203.2628537277481</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>774562.8297237125</v>
+        <v>1718240.055965841</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1386.141734328937</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>765547.439804835</v>
+        <v>1615601.373888271</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>911.9708818498623</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>759244.403233764</v>
+        <v>1602771.12539827</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>1046.24880310383</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>497866.2856494074</v>
+        <v>1050705.393533984</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>135.615340574128</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>486482.2195977009</v>
+        <v>1024104.749335516</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>50.32270471725394</v>
@@ -22456,13 +22456,13 @@
         <v>441233</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35611716.065</v>
+        <v>35611716.06500001</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25007081</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.70954816389526</v>
+        <v>80.70954816389528</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.67545491837646</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>428968.5453314419</v>
+        <v>951596.0604523151</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>683.0979208238161</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>229790.0405976852</v>
+        <v>509751.3553003796</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>200.1341745637325</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>214951.7869639371</v>
+        <v>476561.9260294752</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>534.8355093643613</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>179208.8089058731</v>
+        <v>378205.2882745266</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>38.90622654596869</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>156686.5819728405</v>
+        <v>347583.373545233</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>394.7567411067414</v>
@@ -22852,19 +22852,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>EMGALITY</t>
+          <t>SPIRIVA RESPIMAT</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>145324.4605924341</v>
+        <v>309725.2257094756</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>255.2710766433429</v>
+        <v>353.9048253196112</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -22929,19 +22929,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>SPIRIVA RESPIMAT</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>139620.5649084905</v>
+        <v>307356.6619897448</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>353.9048253196112</v>
+        <v>255.2710766433429</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>135741.6786401494</v>
+        <v>301120.5554322086</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>45.37926051154399</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>116662.5129954038</v>
+        <v>258796.5690657278</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>391.1862481602683</v>
@@ -23125,7 +23125,7 @@
         <v>514</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>18866</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>14164154.06837861</v>
+        <v>30018660.8052422</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>18949.69447095236</v>
@@ -23282,10 +23282,10 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3364040.957073547</v>
+        <v>7096953.168330107</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>718.7317357762591</v>
+        <v>718.7317357762593</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2980310.504077716</v>
+        <v>6611054.745100189</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>5945.443842592063</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>2067344.026415233</v>
+        <v>4586062.200939115</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>6525.318320594901</v>
@@ -23526,14 +23526,14 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>434604.5566323876</v>
+        <v>951596.0604523151</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>687.9725696255854</v>
+        <v>703.6972757804097</v>
       </c>
     </row>
     <row r="54">
@@ -23561,7 +23561,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>41.17788482492599</v>
@@ -23570,16 +23570,16 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -23588,7 +23588,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V54" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W54" s="131" t="n">
         <v>2685.600441370127</v>
@@ -23600,21 +23600,21 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>428968.5453314419</v>
+        <v>929703.5651132767</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>703.6972757804097</v>
+        <v>687.9725696255854</v>
       </c>
     </row>
     <row r="55">
@@ -23692,10 +23692,10 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>365531.7192378346</v>
+        <v>810871.9107325883</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>245.5134350752764</v>
+        <v>245.5134350752765</v>
       </c>
     </row>
     <row r="56">
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>165540.1830268562</v>
+        <v>362642.8076452239</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>381.4998332821</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>162271.5517438948</v>
+        <v>342425.2137484379</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>1428.843708119586</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>0</v>
@@ -23894,13 +23894,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>139218.2263411419</v>
+        <v>308832.7038688332</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>465.8851297185105</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>127768.8161860755</v>
+        <v>279831.3445857477</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>186.2859347078134</v>
@@ -24074,7 +24074,7 @@
         <v>20.903453733182</v>
       </c>
       <c r="V60" s="130" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="W60" s="131" t="n">
         <v>0</v>
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="132" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="AE60" s="121" t="n">
         <v>12</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>106450.448557767</v>
+        <v>234648.7753062839</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>264.1517331178595</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>54909.25537701821</v>
+        <v>121807.1387000384</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>249.402128387031</v>
@@ -24209,7 +24209,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>3.774092554166141</v>
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>303.2145528003117</v>
@@ -24227,7 +24227,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>564.9133635784891</v>
@@ -24248,7 +24248,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>35686.01554623178</v>
+        <v>79163.54748294217</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>43.29829418544201</v>
@@ -24287,7 +24287,7 @@
         <v>5553</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1802.821324481974</v>
+        <v>1802.82132448198</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>1753.114204203743</v>
@@ -24299,22 +24299,22 @@
         <v>2844.950696784313</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>6429.36925984275</v>
+        <v>6429.369259842755</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>1851.880461115068</v>
+        <v>1851.88046111507</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>3076.857772465649</v>
+        <v>3076.857772465648</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>6766.011556755312</v>
+        <v>6766.011556755315</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>1901.212535840979</v>
@@ -24326,10 +24326,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3301.979441896157</v>
+        <v>3301.979441896156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7099.933196522159</v>
+        <v>7099.933196522158</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>34194.96379136435</v>
+        <v>75259.71083130775</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>47.48465002356028</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>34074.63722635455</v>
+        <v>73802.34864922207</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>291.8305813563676</v>
@@ -24454,7 +24454,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>10362.76294094245</v>
@@ -24472,22 +24472,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q65" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R65" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S65" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W65" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X65" s="134" t="n">
         <v>52.89522154413101</v>
@@ -24507,10 +24507,10 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>32595.62235246769</v>
+        <v>72308.01921533378</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>136.7057532332155</v>
+        <v>136.7057532332154</v>
       </c>
     </row>
     <row r="66">
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>32429.44326798675</v>
+        <v>71568.33419485444</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>145.3424453552926</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>31605.02854111495</v>
+        <v>70110.55001007217</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>163.9645358513796</v>
@@ -24698,10 +24698,10 @@
         <v>15667</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>16726.1744960469</v>
+        <v>16726.17449604691</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>200.2485681823899</v>
@@ -24710,7 +24710,7 @@
         <v>3035.538750812163</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>38046.13205183197</v>
+        <v>38046.13205183198</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>13288.69061109529</v>
@@ -24722,7 +24722,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>3271.254361623844</v>
+        <v>3271.254361623843</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>30705.86223329496</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>25780.14254861159</v>
+        <v>57188.99987924073</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>153.9107780087525</v>
@@ -25124,7 +25124,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>0</v>
@@ -25136,7 +25136,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V74" s="130" t="n">
         <v>9.887007747403397</v>
@@ -25377,7 +25377,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="130" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="K78" s="131" t="n">
         <v>0</v>
@@ -25389,10 +25389,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="132" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="P78" s="130" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="Q78" s="131" t="n">
         <v>0</v>
@@ -25404,7 +25404,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="132" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="V78" s="130" t="n">
         <v>9.398797005461862</v>
@@ -26183,7 +26183,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>41.17788482492599</v>
@@ -26192,16 +26192,16 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -26210,7 +26210,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V90" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W90" s="131" t="n">
         <v>2685.600441370127</v>
@@ -26222,7 +26222,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
     </row>
     <row r="91">
@@ -26329,7 +26329,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>0</v>
@@ -26341,7 +26341,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V92" s="130" t="n">
         <v>9.887007747403397</v>
@@ -26451,7 +26451,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L94" s="131" t="n">
         <v>0</v>
@@ -26460,13 +26460,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -26475,7 +26475,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -26597,7 +26597,7 @@
         <v>30.30547604487107</v>
       </c>
       <c r="P96" s="130" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="Q96" s="131" t="n">
         <v>0</v>
@@ -26609,7 +26609,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="132" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="V96" s="130" t="n">
         <v>29.43890635513617</v>
@@ -26719,7 +26719,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>3.774092554166141</v>
@@ -26728,7 +26728,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>303.2145528003117</v>
@@ -26737,7 +26737,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -26746,7 +26746,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>564.9133635784891</v>
@@ -26758,7 +26758,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
     </row>
     <row r="99">
@@ -26783,7 +26783,7 @@
         <v>5955</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1810.995396542639</v>
+        <v>1810.995396542643</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1753.114204203743</v>
@@ -26795,25 +26795,25 @@
         <v>3387.161343351757</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>6979.753978470859</v>
+        <v>6979.753978470862</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>1866.55260272007</v>
+        <v>1866.552602720072</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3691.21780479876</v>
+        <v>3691.217804798759</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>7395.043730693425</v>
+        <v>7395.043730693427</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1924.132424633852</v>
+        <v>1924.132424633854</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1866.517853908823</v>
@@ -26822,10 +26822,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>4002.083765415841</v>
+        <v>4002.08376541584</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>7822.957408834715</v>
+        <v>7822.957408834716</v>
       </c>
     </row>
     <row r="100">
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>10362.76294094245</v>
@@ -26940,22 +26940,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q101" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R101" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S101" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W101" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X101" s="134" t="n">
         <v>52.89522154413101</v>
@@ -27125,7 +27125,7 @@
         <v>16747.82759709495</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>200.2485681823899</v>
@@ -27134,7 +27134,7 @@
         <v>3577.749397379607</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>39152.2064460149</v>
+        <v>39152.20644601491</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>13321.20947909905</v>
@@ -27146,7 +27146,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>3885.614393956954</v>
+        <v>3885.614393956953</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>31967.10116596494</v>
@@ -27161,7 +27161,7 @@
         <v>129.0666188664547</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>4201.890485304369</v>
+        <v>4201.890485304368</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>29537.67339702922</v>
@@ -28153,7 +28153,7 @@
         <v>35031</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>738222.6000000001</v>
+        <v>738222.6</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>752400</v>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>10848588.39050994</v>
+        <v>23258824.1613084</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>14046.4886195905</v>
@@ -28230,13 +28230,13 @@
         <v>6424</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>370464.4899999999</v>
+        <v>370464.49</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>492332</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>57.66881849315067</v>
+        <v>57.6688184931507</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>76.63947696139476</v>
@@ -28274,10 +28274,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>4556554.978241712</v>
+        <v>9704281.963402636</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>5867.471866301445</v>
+        <v>5867.471866301444</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28351,7 +28351,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>2426687.816200567</v>
+        <v>5423526.294575613</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>6824.086162599673</v>
@@ -28390,7 +28390,7 @@
         <v>1257088</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>26.86525550427844</v>
+        <v>26.86525550427843</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>30.21555619651956</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1278546.02373184</v>
+        <v>2723011.14444064</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>124.4909448484157</v>
@@ -28461,7 +28461,7 @@
         <v>514</v>
       </c>
       <c r="E29" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F29" s="61" t="n">
         <v>18866</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>984840.4136955449</v>
+        <v>2201069.228592134</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1940.3377889499</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>939863.2018768771</v>
+        <v>2001694.053601917</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>207.8023572318635</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>893077.1896544808</v>
+        <v>1902023.108439393</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1012.287678853347</v>
@@ -28707,19 +28707,19 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>872627.0500916673</v>
+        <v>1900615.65816561</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>1161.336171445251</v>
+        <v>1450.015145446814</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -28784,19 +28784,19 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>TRULICITY</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>850406.2874302724</v>
+        <v>1859240.644392266</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>1450.015145446814</v>
+        <v>1161.336171445251</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>630970.5459087703</v>
+        <v>1343823.215145938</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>160.1194938565857</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>631153.9581943477</v>
+        <v>1338904.5361324</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>59.58359206637017</v>
@@ -28980,13 +28980,13 @@
         <v>441233</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35611716.065</v>
+        <v>35611716.06500001</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25007081</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.70954816389526</v>
+        <v>80.70954816389528</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.67545491837646</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>447169.7211032961</v>
+        <v>999402.0344730334</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>680.8983455187634</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>250159.5540040527</v>
+        <v>559094.1323076852</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>205.7079113253324</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>192842.1910744352</v>
+        <v>410709.842013614</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>39.70692345325912</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>167382.442740591</v>
+        <v>357127.8166343408</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>274.1764525795489</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>146562.6234130948</v>
+        <v>327560.1569251068</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>46.64307291679049</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>125552.8104760158</v>
+        <v>280604.272386663</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>255.6652448323512</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>121132.368215234</v>
+        <v>270724.8043005949</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>388.1193479746918</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>111085.6733788387</v>
+        <v>243322.0977264049</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>151.6245874764233</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>104347.41443705</v>
+        <v>227726.2504442609</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>209.1982181531818</v>
@@ -29649,7 +29649,7 @@
         <v>514</v>
       </c>
       <c r="E45" s="61" t="n">
-        <v>8324.759999999998</v>
+        <v>8324.76</v>
       </c>
       <c r="F45" s="61" t="n">
         <v>18866</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>17170847.6084978</v>
+        <v>36724369.8775427</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>22087.63381749754</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3958366.704285002</v>
+        <v>8425108.09811699</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>777.3137119705132</v>
@@ -29852,7 +29852,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2553281.28119282</v>
+        <v>5706456.377927617</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>7699.875618301982</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1908346.805680422</v>
+        <v>4264992.30568135</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>3913.107131187896</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>496402.7859005958</v>
+        <v>1070703.661086076</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>737.2381876409371</v>
@@ -30085,7 +30085,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>41.17788482492599</v>
@@ -30094,16 +30094,16 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -30112,7 +30112,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V54" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W54" s="131" t="n">
         <v>2685.600441370127</v>
@@ -30124,7 +30124,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>447169.7211032961</v>
+        <v>999402.0344730334</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>701.4313705523967</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>396722.1774171474</v>
+        <v>886654.2892327921</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>252.3509842421229</v>
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>161828.2428229158</v>
+        <v>344609.9268040808</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>1362.130995387483</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>144552.2903838988</v>
+        <v>323067.1628234721</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>462.2325903015174</v>
@@ -30409,7 +30409,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>0</v>
@@ -30418,13 +30418,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -30433,7 +30433,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>112779.7341875542</v>
+        <v>250253.3072551585</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>261.541913994655</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>111085.6733788387</v>
+        <v>243322.0977264049</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>163.6270054127749</v>
@@ -30598,7 +30598,7 @@
         <v>20.903453733182</v>
       </c>
       <c r="V60" s="130" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="W60" s="131" t="n">
         <v>0</v>
@@ -30610,7 +30610,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="132" t="n">
-        <v>20.04010934967431</v>
+        <v>20.0401093496743</v>
       </c>
       <c r="AE60" s="121" t="n">
         <v>12</v>
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>73357.38249300298</v>
+        <v>159560.4746508019</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>178.8597661354401</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>52645.00752229179</v>
+        <v>117658.967366605</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>220.7009314522514</v>
@@ -30733,7 +30733,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>3.774092554166141</v>
@@ -30742,7 +30742,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>303.2145528003117</v>
@@ -30751,7 +30751,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R62" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S62" s="131" t="n">
         <v>0</v>
@@ -30760,7 +30760,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>564.9133635784891</v>
@@ -30772,7 +30772,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
       <c r="AE62" s="121" t="n">
         <v>14</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>41037.11839871943</v>
+        <v>91021.05271381944</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>53.27350370793251</v>
@@ -30811,7 +30811,7 @@
         <v>5553</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1802.821324481974</v>
+        <v>1802.82132448198</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>1753.114204203743</v>
@@ -30823,22 +30823,22 @@
         <v>2844.950696784313</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>6429.36925984275</v>
+        <v>6429.369259842755</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>1851.880461115068</v>
+        <v>1851.88046111507</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>3076.857772465649</v>
+        <v>3076.857772465648</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>6766.011556755312</v>
+        <v>6766.011556755315</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>1901.212535840979</v>
@@ -30850,10 +30850,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3301.979441896157</v>
+        <v>3301.979441896156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>7099.933196522159</v>
+        <v>7099.933196522158</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,10 +30864,10 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>36439.43978061579</v>
+        <v>81440.33133985953</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>41.27669682992372</v>
+        <v>41.27669682992371</v>
       </c>
     </row>
     <row r="64">
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2942.903652687994</v>
+        <v>2942.903652687993</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -30945,7 +30945,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>35000.87162130811</v>
+        <v>78225.2032189461</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>138.1616695051492</v>
@@ -30978,7 +30978,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K65" s="134" t="n">
         <v>10362.76294094245</v>
@@ -30996,22 +30996,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q65" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R65" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S65" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W65" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X65" s="134" t="n">
         <v>52.89522154413101</v>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>33298.05883948253</v>
+        <v>72724.3037810036</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>278.2050115128387</v>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>29509.45096037862</v>
+        <v>65952.15179869482</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>166.4437326620052</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>18043.86410130946</v>
+        <v>40327.13674823695</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>169.0632073884084</v>
@@ -31222,10 +31222,10 @@
         <v>15667</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>16726.1744960469</v>
+        <v>16726.17449604691</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>200.2485681823899</v>
@@ -31234,7 +31234,7 @@
         <v>3035.538750812163</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>38046.13205183197</v>
+        <v>38046.13205183198</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>13288.69061109529</v>
@@ -31246,7 +31246,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>3271.254361623844</v>
+        <v>3271.254361623843</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>30705.86223329496</v>
@@ -31275,7 +31275,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>15012.24246250262</v>
+        <v>32216.68649900575</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>180.116495257849</v>
@@ -31648,7 +31648,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>0</v>
@@ -31660,7 +31660,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V74" s="130" t="n">
         <v>9.887007747403397</v>
@@ -31901,7 +31901,7 @@
         <v>12</v>
       </c>
       <c r="J78" s="130" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="K78" s="131" t="n">
         <v>0</v>
@@ -31913,10 +31913,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="132" t="n">
-        <v>5.041984669506058</v>
+        <v>5.041984669506059</v>
       </c>
       <c r="P78" s="130" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="Q78" s="131" t="n">
         <v>0</v>
@@ -31928,7 +31928,7 @@
         <v>0</v>
       </c>
       <c r="T78" s="132" t="n">
-        <v>8.219499498426924</v>
+        <v>8.219499498426925</v>
       </c>
       <c r="V78" s="130" t="n">
         <v>9.398797005461862</v>
@@ -32707,7 +32707,7 @@
         <v>4309.055790096152</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>2633.712474131682</v>
+        <v>2633.712474131684</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>41.17788482492599</v>
@@ -32716,16 +32716,16 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>6983.94614905276</v>
+        <v>6983.946149052762</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>4426.864505889944</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>2655.231683498989</v>
+        <v>2655.231683498988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>41.77219377794791</v>
+        <v>41.7721937779479</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -32734,7 +32734,7 @@
         <v>7123.86838316688</v>
       </c>
       <c r="V90" s="130" t="n">
-        <v>4569.054509830285</v>
+        <v>4569.054509830286</v>
       </c>
       <c r="W90" s="131" t="n">
         <v>2685.600441370127</v>
@@ -32746,7 +32746,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>7297.077783249791</v>
+        <v>7297.077783249792</v>
       </c>
     </row>
     <row r="91">
@@ -32853,7 +32853,7 @@
         <v>8.437044317872898</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>0</v>
@@ -32865,7 +32865,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="132" t="n">
-        <v>9.62722690033455</v>
+        <v>9.627226900334554</v>
       </c>
       <c r="V92" s="130" t="n">
         <v>9.887007747403397</v>
@@ -32975,7 +32975,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="131" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="L94" s="131" t="n">
         <v>0</v>
@@ -32984,13 +32984,13 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5.989558841218019</v>
+        <v>5.98955884121802</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -32999,7 +32999,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>5.972608389697371</v>
+        <v>5.972608389697372</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -33121,7 +33121,7 @@
         <v>30.30547604487107</v>
       </c>
       <c r="P96" s="130" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="Q96" s="131" t="n">
         <v>0</v>
@@ -33133,7 +33133,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="132" t="n">
-        <v>29.12295323160892</v>
+        <v>29.12295323160893</v>
       </c>
       <c r="V96" s="130" t="n">
         <v>29.43890635513617</v>
@@ -33243,7 +33243,7 @@
         <v>312.9454002673965</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>604.7983318051241</v>
+        <v>604.7983318051243</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>3.774092554166141</v>
@@ -33252,7 +33252,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>921.5178246266867</v>
+        <v>921.5178246266869</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>303.2145528003117</v>
@@ -33261,7 +33261,7 @@
         <v>585.4024493041337</v>
       </c>
       <c r="R98" s="131" t="n">
-        <v>3.653057405954034</v>
+        <v>3.653057405954032</v>
       </c>
       <c r="S98" s="131" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
         <v>892.2700595103995</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>292.8977883456756</v>
+        <v>292.8977883456755</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>564.9133635784891</v>
@@ -33282,7 +33282,7 @@
         <v>0</v>
       </c>
       <c r="Z98" s="132" t="n">
-        <v>861.3363523209104</v>
+        <v>861.3363523209102</v>
       </c>
     </row>
     <row r="99">
@@ -33307,7 +33307,7 @@
         <v>5955</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1810.995396542639</v>
+        <v>1810.995396542643</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1753.114204203743</v>
@@ -33319,25 +33319,25 @@
         <v>3387.161343351757</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>6979.753978470859</v>
+        <v>6979.753978470862</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>1866.55260272007</v>
+        <v>1866.552602720072</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1807.940878959245</v>
+        <v>1807.940878959247</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>29.33244421534945</v>
+        <v>29.33244421534948</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3691.21780479876</v>
+        <v>3691.217804798759</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>7395.043730693425</v>
+        <v>7395.043730693427</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>1924.132424633852</v>
+        <v>1924.132424633854</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1866.517853908823</v>
@@ -33346,10 +33346,10 @@
         <v>30.22336487619961</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>4002.083765415841</v>
+        <v>4002.08376541584</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>7822.957408834715</v>
+        <v>7822.957408834716</v>
       </c>
     </row>
     <row r="100">
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>3557.263685021104</v>
+        <v>3557.263685021103</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33446,7 +33446,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="133" t="n">
-        <v>10276.08848982602</v>
+        <v>10276.08848982601</v>
       </c>
       <c r="K101" s="134" t="n">
         <v>10362.76294094245</v>
@@ -33464,22 +33464,22 @@
         <v>6685.827637556781</v>
       </c>
       <c r="Q101" s="134" t="n">
-        <v>6000.820684483488</v>
+        <v>6000.820684483487</v>
       </c>
       <c r="R101" s="134" t="n">
-        <v>72.88760785302993</v>
+        <v>72.88760785302992</v>
       </c>
       <c r="S101" s="134" t="n">
         <v>194.3965891581948</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>12953.9325190515</v>
+        <v>12953.93251905149</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>5418.542475273394</v>
       </c>
       <c r="W101" s="134" t="n">
-        <v>3958.184650767316</v>
+        <v>3958.184650767315</v>
       </c>
       <c r="X101" s="134" t="n">
         <v>52.89522154413101</v>
@@ -33649,7 +33649,7 @@
         <v>16747.82759709495</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>15360.37750992421</v>
+        <v>15360.37750992422</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>200.2485681823899</v>
@@ -33658,7 +33658,7 @@
         <v>3577.749397379607</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>39152.2064460149</v>
+        <v>39152.20644601491</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>13321.20947909905</v>
@@ -33670,7 +33670,7 @@
         <v>147.6453032522813</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>3885.614393956954</v>
+        <v>3885.614393956953</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>31967.10116596494</v>
@@ -33685,7 +33685,7 @@
         <v>129.0666188664547</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>4201.890485304369</v>
+        <v>4201.890485304368</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>29537.67339702922</v>
